--- a/DesignTable/Data/Table/Tables/AtlasData.xlsx
+++ b/DesignTable/Data/Table/Tables/AtlasData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectT\DesignTable\Data\Table\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0995889-601F-45B1-B746-23D8D0386936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ADB0318-2AC8-4DCF-B8E6-4A11451069B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3F4DC61C-DF7F-4950-B9C6-A6313E9C3BA7}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3F4DC61C-DF7F-4950-B9C6-A6313E9C3BA7}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AtlasType</t>
   </si>
   <si>
@@ -101,6 +97,14 @@
   </si>
   <si>
     <t>Assets/BundleRes/SpriteAtlas/NewSpriteAtlas.spriteatlas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FieldNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TableId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -158,7 +162,11 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -173,7 +181,7 @@
 
 <file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
 <MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
-  <Schema ID="Schema1">
+  <Schema ID="Schema2">
     <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
       <xsd:element nillable="true" name="AtlasData">
         <xsd:complexType>
@@ -188,6 +196,7 @@
                 <xsd:attribute name="EnumID" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="IDRule" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="StringHashIds" form="unqualified" type="xsd:string"/>
+                <xsd:attribute name="FieldNo" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="TableId" form="unqualified" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
@@ -204,7 +213,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="1" Name="AtlasData_맵" RootElement="AtlasData" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="4" Name="AtlasData_맵" RootElement="AtlasData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -213,10 +222,10 @@
   <autoFilter ref="A1:B2" xr:uid="{13BD990D-B10A-4799-B394-70076236F817}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{3E14796D-9F90-41FD-8685-10B2F06916CA}" uniqueName="AtlasType" name="AtlasType">
-      <xmlColumnPr mapId="1" xpath="/AtlasData/record/AtlasType" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/AtlasData/record/AtlasType" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{742E6A75-7DEA-4AAE-B8CF-CB3FCCBBFB7B}" uniqueName="Path" name="Path">
-      <xmlColumnPr mapId="1" xpath="/AtlasData/record/Path" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/AtlasData/record/Path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -224,35 +233,38 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7B4B12F9-7C42-4143-8B3D-BFDB82DEDFC3}" name="표1" displayName="표1" ref="A1:I3" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:I3" xr:uid="{7B4B12F9-7C42-4143-8B3D-BFDB82DEDFC3}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7B4B12F9-7C42-4143-8B3D-BFDB82DEDFC3}" name="표1" displayName="표1" ref="A1:J3" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:J3" xr:uid="{7B4B12F9-7C42-4143-8B3D-BFDB82DEDFC3}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9AC35F50-B3BB-4A8A-81B2-1722DCB2A5CE}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="1" xpath="/AtlasData/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{EB278A5B-ED8E-4AA2-BD5E-B1CE80E221FF}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="1" xpath="/AtlasData/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{CC864C3D-D82D-4B7D-805A-41EB891F0133}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="1" xpath="/AtlasData/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7EF56112-C93B-49FB-A525-847DB5DF9C2E}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="1" xpath="/AtlasData/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{7BC6B606-3953-4A21-B87D-B1617FAF3191}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="1" xpath="/AtlasData/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{D04FB710-3E13-48FC-BBB9-1D63CE687FA1}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="1" xpath="/AtlasData/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{CD2A9EDE-3E08-43D3-A0E8-75327CB4BA61}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="1" xpath="/AtlasData/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{7FB2C5DD-4B14-49C8-AA33-FAEDB62D5E59}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="1" xpath="/AtlasData/verify/@StringHashIds" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{5A8A3B69-FC59-43C8-8C40-8CA28ACF7E75}" uniqueName="TableId" name="TableID">
-      <xmlColumnPr mapId="1" xpath="/AtlasData/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@StringHashIds" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{5A8A3B69-FC59-43C8-8C40-8CA28ACF7E75}" uniqueName="FieldNo" name="FieldNo">
+      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@FieldNo" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{0CE418AC-4A34-4DC2-91D8-E190D96A4DC7}" uniqueName="TableId" name="TableId" dataDxfId="0">
+      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -566,18 +578,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -591,10 +603,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F027E9-E622-42B3-9B56-5A93A40C5893}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -620,64 +632,73 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1023</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1">
         <v>1023</v>
       </c>
     </row>

--- a/DesignTable/Data/Table/Tables/AtlasData.xlsx
+++ b/DesignTable/Data/Table/Tables/AtlasData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ADB0318-2AC8-4DCF-B8E6-4A11451069B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79CDA281-AFE3-4CF5-AFB9-8D44CA9A5869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3F4DC61C-DF7F-4950-B9C6-A6313E9C3BA7}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="verify" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -213,7 +213,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="4" Name="AtlasData_맵" RootElement="AtlasData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="7" Name="AtlasData_맵" RootElement="AtlasData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -222,10 +222,10 @@
   <autoFilter ref="A1:B2" xr:uid="{13BD990D-B10A-4799-B394-70076236F817}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{3E14796D-9F90-41FD-8685-10B2F06916CA}" uniqueName="AtlasType" name="AtlasType">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/record/AtlasType" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/record/AtlasType" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{742E6A75-7DEA-4AAE-B8CF-CB3FCCBBFB7B}" uniqueName="Path" name="Path">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/record/Path" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/record/Path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -237,34 +237,34 @@
   <autoFilter ref="A1:J3" xr:uid="{7B4B12F9-7C42-4143-8B3D-BFDB82DEDFC3}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9AC35F50-B3BB-4A8A-81B2-1722DCB2A5CE}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{EB278A5B-ED8E-4AA2-BD5E-B1CE80E221FF}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{CC864C3D-D82D-4B7D-805A-41EB891F0133}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7EF56112-C93B-49FB-A525-847DB5DF9C2E}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{7BC6B606-3953-4A21-B87D-B1617FAF3191}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{D04FB710-3E13-48FC-BBB9-1D63CE687FA1}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{CD2A9EDE-3E08-43D3-A0E8-75327CB4BA61}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{7FB2C5DD-4B14-49C8-AA33-FAEDB62D5E59}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{5A8A3B69-FC59-43C8-8C40-8CA28ACF7E75}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{0CE418AC-4A34-4DC2-91D8-E190D96A4DC7}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="4" xpath="/AtlasData/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/AtlasData.xlsx
+++ b/DesignTable/Data/Table/Tables/AtlasData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79CDA281-AFE3-4CF5-AFB9-8D44CA9A5869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD976AF5-E506-4EEB-83DE-ED2FA22BD1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3F4DC61C-DF7F-4950-B9C6-A6313E9C3BA7}"/>
   </bookViews>
@@ -213,7 +213,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="7" Name="AtlasData_맵" RootElement="AtlasData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="9" Name="AtlasData_맵" RootElement="AtlasData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -222,10 +222,10 @@
   <autoFilter ref="A1:B2" xr:uid="{13BD990D-B10A-4799-B394-70076236F817}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{3E14796D-9F90-41FD-8685-10B2F06916CA}" uniqueName="AtlasType" name="AtlasType">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/record/AtlasType" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/record/AtlasType" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{742E6A75-7DEA-4AAE-B8CF-CB3FCCBBFB7B}" uniqueName="Path" name="Path">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/record/Path" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/record/Path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -237,34 +237,34 @@
   <autoFilter ref="A1:J3" xr:uid="{7B4B12F9-7C42-4143-8B3D-BFDB82DEDFC3}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9AC35F50-B3BB-4A8A-81B2-1722DCB2A5CE}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{EB278A5B-ED8E-4AA2-BD5E-B1CE80E221FF}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{CC864C3D-D82D-4B7D-805A-41EB891F0133}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7EF56112-C93B-49FB-A525-847DB5DF9C2E}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{7BC6B606-3953-4A21-B87D-B1617FAF3191}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{D04FB710-3E13-48FC-BBB9-1D63CE687FA1}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{CD2A9EDE-3E08-43D3-A0E8-75327CB4BA61}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{7FB2C5DD-4B14-49C8-AA33-FAEDB62D5E59}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{5A8A3B69-FC59-43C8-8C40-8CA28ACF7E75}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{0CE418AC-4A34-4DC2-91D8-E190D96A4DC7}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="7" xpath="/AtlasData/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/AtlasData.xlsx
+++ b/DesignTable/Data/Table/Tables/AtlasData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD976AF5-E506-4EEB-83DE-ED2FA22BD1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{555D1677-ABA9-482D-AC8A-20BC20798247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3F4DC61C-DF7F-4950-B9C6-A6313E9C3BA7}"/>
   </bookViews>
@@ -213,7 +213,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="9" Name="AtlasData_맵" RootElement="AtlasData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="10" Name="AtlasData_맵" RootElement="AtlasData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -222,10 +222,10 @@
   <autoFilter ref="A1:B2" xr:uid="{13BD990D-B10A-4799-B394-70076236F817}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{3E14796D-9F90-41FD-8685-10B2F06916CA}" uniqueName="AtlasType" name="AtlasType">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/record/AtlasType" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/record/AtlasType" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{742E6A75-7DEA-4AAE-B8CF-CB3FCCBBFB7B}" uniqueName="Path" name="Path">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/record/Path" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/record/Path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -237,34 +237,34 @@
   <autoFilter ref="A1:J3" xr:uid="{7B4B12F9-7C42-4143-8B3D-BFDB82DEDFC3}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9AC35F50-B3BB-4A8A-81B2-1722DCB2A5CE}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{EB278A5B-ED8E-4AA2-BD5E-B1CE80E221FF}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{CC864C3D-D82D-4B7D-805A-41EB891F0133}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7EF56112-C93B-49FB-A525-847DB5DF9C2E}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{7BC6B606-3953-4A21-B87D-B1617FAF3191}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{D04FB710-3E13-48FC-BBB9-1D63CE687FA1}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{CD2A9EDE-3E08-43D3-A0E8-75327CB4BA61}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{7FB2C5DD-4B14-49C8-AA33-FAEDB62D5E59}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{5A8A3B69-FC59-43C8-8C40-8CA28ACF7E75}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{0CE418AC-4A34-4DC2-91D8-E190D96A4DC7}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="9" xpath="/AtlasData/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="10" xpath="/AtlasData/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
